--- a/Config/HandScoreConfig.xlsx
+++ b/Config/HandScoreConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="12645" windowHeight="9090"/>
+    <workbookView windowWidth="14610" windowHeight="9165"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -76,7 +76,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>散牌</t>
+    <t>高牌</t>
   </si>
   <si>
     <t>HighCard</t>
@@ -103,7 +103,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>金花</t>
+    <t>同花</t>
   </si>
   <si>
     <t>Flush</t>
@@ -115,7 +115,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>顺金</t>
+    <t>同花顺</t>
   </si>
   <si>
     <t>StraightFlush</t>
@@ -1103,7 +1103,7 @@
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="4.01666666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="1"/>
+    <col min="3" max="3" width="6.84166666666667" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.2333333333333" style="1" customWidth="1"/>
     <col min="5" max="5" width="18.5833333333333" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>

--- a/Config/HandScoreConfig.xlsx
+++ b/Config/HandScoreConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14610" windowHeight="9165"/>
+    <workbookView windowWidth="19995" windowHeight="11520"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
   <si>
     <t>##var</t>
   </si>
@@ -94,22 +94,19 @@
     <t>3</t>
   </si>
   <si>
+    <t>同花</t>
+  </si>
+  <si>
+    <t>Flush</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>顺子</t>
   </si>
   <si>
     <t>Straight</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>同花</t>
-  </si>
-  <si>
-    <t>Flush</t>
-  </si>
-  <si>
-    <t>3.5</t>
   </si>
   <si>
     <t>5</t>
@@ -598,153 +595,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1101,12 +1098,12 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="1" customWidth="1"/>
     <col min="2" max="2" width="4.01666666666667" style="1" customWidth="1"/>
     <col min="3" max="3" width="6.84166666666667" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.2333333333333" style="1" customWidth="1"/>
     <col min="5" max="5" width="18.5833333333333" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="6" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1160,8 +1157,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:5">
-      <c r="A5" s="1"/>
+    <row r="5" spans="1:5">
       <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
@@ -1199,8 +1195,8 @@
       <c r="D7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>19</v>
+      <c r="E7" s="1">
+        <v>2.5</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1213,36 +1209,36 @@
       <c r="D8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>25</v>
+      <c r="E8" s="1">
+        <v>3.5</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="B9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" t="s">
         <v>27</v>
       </c>
-      <c r="D9" t="s">
-        <v>28</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="B10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E10" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Config/HandScoreConfig.xlsx
+++ b/Config/HandScoreConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19995" windowHeight="11520"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -43,6 +43,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>Level</t>
+  </si>
+  <si>
     <t>Type</t>
   </si>
   <si>
@@ -65,6 +68,9 @@
   </si>
   <si>
     <t>名字</t>
+  </si>
+  <si>
+    <t>牌型顺位</t>
   </si>
   <si>
     <t>牌型</t>
@@ -1095,18 +1101,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9" style="1" customWidth="1"/>
     <col min="2" max="2" width="4.01666666666667" style="1" customWidth="1"/>
     <col min="3" max="3" width="6.84166666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.2333333333333" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.5833333333333" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.35833333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.2333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5833333333333" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1122,123 +1129,150 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:6">
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="1">
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:6">
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="1">
         <v>3.5</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:6">
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>25</v>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:6">
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Config/HandScoreConfig.xlsx
+++ b/Config/HandScoreConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="14445" windowHeight="11505"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
